--- a/results/Int Task Remove ACC 0.2/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC 0.2/Rando_4_permute.xlsx
@@ -440,783 +440,783 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7083050847457627</v>
+        <v>0.6935691722427906</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7076420637885941</v>
+        <v>0.6714802486328589</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7074650996909072</v>
+        <v>0.6810166094901667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7278866206990251</v>
+        <v>0.6850096803777046</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7237016405692742</v>
+        <v>0.7146411467001801</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7090404537889338</v>
+        <v>0.716555483849054</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7179837641384463</v>
+        <v>0.7070065554838491</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7096287490234707</v>
+        <v>0.7239234401005401</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.685682891206141</v>
+        <v>0.7451149757141402</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6906929112462212</v>
+        <v>0.7447759926632926</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7019493223735607</v>
+        <v>0.7300951054651676</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7039383852450665</v>
+        <v>0.7275051798512279</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7104364661526443</v>
+        <v>0.7304813015862233</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7137814612275398</v>
+        <v>0.7273581060425937</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6826320437485141</v>
+        <v>0.7254862266906694</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6949203491729221</v>
+        <v>0.727049013280799</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7208253795727048</v>
+        <v>0.727049013280799</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7228443327332632</v>
+        <v>0.7252070242179274</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7459203152066844</v>
+        <v>0.7198454536191026</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7534054549777521</v>
+        <v>0.6891647702184029</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7592405149281614</v>
+        <v>0.6889579158316633</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7628174994055908</v>
+        <v>0.673307292551204</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7577925342209844</v>
+        <v>0.6749723175163886</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7244526340817228</v>
+        <v>0.6765201589619918</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7236849971128698</v>
+        <v>0.6714778709962297</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7225658095852723</v>
+        <v>0.652616758941612</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7153527393770591</v>
+        <v>0.653985258652899</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7068380829455522</v>
+        <v>0.653985258652899</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7051981929961618</v>
+        <v>0.6522030501681328</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6856190346795286</v>
+        <v>0.6403984239665772</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6863717265038551</v>
+        <v>0.6368465745049421</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6719449067626779</v>
+        <v>0.634361944227438</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.668083964539248</v>
+        <v>0.6345239631805984</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6698685506606433</v>
+        <v>0.6542101151455453</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6399184810298564</v>
+        <v>0.6233847355728406</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.628941272375259</v>
+        <v>0.614074929520057</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5892598756835705</v>
+        <v>0.6159019734384023</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5892598756835705</v>
+        <v>0.6090924221324004</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5833351448660031</v>
+        <v>0.6045786488230699</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5845864610577087</v>
+        <v>0.5912435039570667</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5861618151557352</v>
+        <v>0.6005210420841683</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.606837403620801</v>
+        <v>0.5638409021432695</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6078543527733433</v>
+        <v>0.5280299582215278</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6313990693250908</v>
+        <v>0.5280299582215278</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6297765021568561</v>
+        <v>0.52374749498998</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6498913080398084</v>
+        <v>0.5250735369043171</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6340654189735403</v>
+        <v>0.5217135966848953</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6299724873475765</v>
+        <v>0.5246622057674671</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6257450494208756</v>
+        <v>0.5049210284976733</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6352263849733365</v>
+        <v>0.5356866274922727</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6134662545429843</v>
+        <v>0.5101205801433375</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6154678849223871</v>
+        <v>0.5108284365340852</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6271828402567847</v>
+        <v>0.5223090248293196</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.633105193437723</v>
+        <v>0.5223090248293196</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6340049590706838</v>
+        <v>0.5155663870113107</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6288927006555484</v>
+        <v>0.510404537889338</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6288927006555484</v>
+        <v>0.498906626812948</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6288927006555484</v>
+        <v>0.4976529329846133</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6288927006555484</v>
+        <v>0.5301654155769165</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6112727149213681</v>
+        <v>0.5334105499133861</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5999439557080262</v>
+        <v>0.5417828878095173</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.52415033456744</v>
+        <v>0.5613871811419449</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5063360619544173</v>
+        <v>0.5900662341632418</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5098430759824735</v>
+        <v>0.5775608844808261</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5098430759824735</v>
+        <v>0.5768829183791312</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5053340579464013</v>
+        <v>0.5823616724975375</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5013260419143372</v>
+        <v>0.5866213783499201</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5001620189531606</v>
+        <v>0.5737573451988723</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5001620189531606</v>
+        <v>0.5601280527156006</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5003090927617948</v>
+        <v>0.564784144560307</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5</v>
+        <v>0.5683485615298394</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.500501002004008</v>
+        <v>0.5696447131551238</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.500501002004008</v>
+        <v>0.5741836214802487</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5</v>
+        <v>0.5822271661968004</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5</v>
+        <v>0.5817261641927923</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5</v>
+        <v>0.6232526069087327</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5</v>
+        <v>0.622265548045243</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5</v>
+        <v>0.4983774328317652</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1226,47 +1226,47 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5</v>
+        <v>0.500501002004008</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.500501002004008</v>
+        <v>0.4996610169491525</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5</v>
+        <v>0.4996610169491525</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>0.4996610169491525</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1276,7 +1276,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1286,7 +1286,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1296,7 +1296,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1306,7 +1306,7 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1316,7 +1316,7 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B90" t="n">
